--- a/data/Fall2018/db1-7_missing-data-runs/db2/14-gene_25-edges_db2_Sigmoid_estimation_missing-values.xlsx
+++ b/data/Fall2018/db1-7_missing-data-runs/db2/14-gene_25-edges_db2_Sigmoid_estimation_missing-values.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lmu0-my.sharepoint.com/personal/nchun2_lion_lmu_edu/Documents/Documents/GitHub/DahlquistLabTest/data/Fall2018/db1-7_missing-data-runs/db2/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_D06A42C86897070689768DF55BA3AFE5D4C4F892" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F480921-7589-405B-81FF-C487C4A7E496}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="120" windowWidth="13395" windowHeight="9015" firstSheet="4" activeTab="9"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="production_rates" sheetId="1" r:id="rId1"/>
@@ -19,7 +25,20 @@
     <sheet name="optimization_parameters" sheetId="11" r:id="rId10"/>
     <sheet name="threshold_b" sheetId="12" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="145621" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -155,7 +174,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -201,22 +220,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -232,9 +246,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -272,7 +286,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -344,7 +358,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -517,11 +531,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -529,115 +543,115 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="4">
         <v>0.20100000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
         <v>0.19259999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>0.32240000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>0.27179999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>0.4078</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>0.19800000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>0.69320000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>0.28299999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>0.32240000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>0.17319999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>0.72960000000000003</v>
       </c>
     </row>
@@ -647,354 +661,192 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>2E-3</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>100000000</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>100000000</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="2">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="10">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="4">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14">
         <v>15</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14">
         <v>30</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14">
         <v>60</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>5</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16">
         <v>10</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16">
         <v>15</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16">
         <v>20</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16">
         <v>25</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16">
         <v>30</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16">
         <v>35</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16">
         <v>40</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16">
         <v>45</v>
       </c>
-      <c r="L16" s="2">
+      <c r="L16">
         <v>50</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16">
         <v>55</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16">
         <v>60</v>
       </c>
     </row>
@@ -1004,11 +856,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -1016,115 +868,115 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15">
         <v>0</v>
       </c>
     </row>
@@ -1134,11 +986,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -1146,131 +998,131 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2">
         <v>0.10050000000000001</v>
       </c>
-      <c r="D2" s="6"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3">
         <v>9.6299999999999997E-2</v>
       </c>
-      <c r="D3" s="6"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4">
         <v>0.16120000000000001</v>
       </c>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5">
         <v>0.13589999999999999</v>
       </c>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8">
         <v>0.2039</v>
       </c>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10">
         <v>0.34660000000000002</v>
       </c>
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12">
         <v>0.14149999999999999</v>
       </c>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13">
         <v>0.16120000000000001</v>
       </c>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14">
         <v>8.6599999999999996E-2</v>
       </c>
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15">
         <v>0.36480000000000001</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1279,11 +1131,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -1327,619 +1179,619 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2">
         <v>-0.13730000000000001</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2">
         <v>-9.9699999999999997E-2</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2">
         <v>1.2385999999999999</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2">
         <v>1.3909</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2">
         <v>-0.4224</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2">
         <v>0.54610000000000003</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2">
         <v>1.0285</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2">
         <v>1.2338</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2">
         <v>2.2159</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2">
         <v>2.1796000000000002</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2">
         <v>0.84470000000000001</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2">
         <v>2.4687000000000001</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2">
         <v>1.4784999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3">
         <v>0.50639999999999996</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3">
         <v>0.89049999999999996</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3">
         <v>-0.1242</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3">
         <v>-1.1405000000000001</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3">
         <v>0.38369999999999999</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3">
         <v>0.85250000000000004</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3">
         <v>9.8799999999999999E-2</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3">
         <v>-0.32729999999999998</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3">
         <v>-0.29820000000000002</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3">
         <v>-0.315</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3">
         <v>-0.59989999999999999</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3">
         <v>-0.94469999999999998</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3">
         <v>-0.35849999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4">
         <v>-1.3141</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4">
         <v>0.39389999999999997</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4">
         <v>0.1439</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4">
         <v>-0.51329999999999998</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4">
         <v>-0.70040000000000002</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4">
         <v>-0.2467</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4">
         <v>1.4085000000000001</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4">
         <v>0.97330000000000005</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4">
         <v>0.65039999999999998</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4">
         <v>0.20250000000000001</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4">
         <v>0.89239999999999997</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4">
         <v>0.90069999999999995</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4">
         <v>0.1953</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5">
         <v>0.51380000000000003</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5">
         <v>1.9214</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5">
         <v>-0.88590000000000002</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5">
         <v>-2.6541999999999999</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5">
         <v>0.13800000000000001</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5">
         <v>1.5184</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5">
         <v>0.27939999999999998</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5">
         <v>-2.5135000000000001</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5">
         <v>-1.1181000000000001</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5">
         <v>0.2225</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5">
         <v>-1.0353000000000001</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5">
         <v>-0.2074</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5">
         <v>-1.8463000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6">
         <v>0.30580000000000002</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6">
         <v>0.2392</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6">
         <v>1.8398000000000001</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6">
         <v>1.2493000000000001</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6">
         <v>-0.95250000000000001</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6">
         <v>1.405</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6">
         <v>1.3109</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6">
         <v>1.2568999999999999</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6">
         <v>1.9007000000000001</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6">
         <v>1.4816</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6">
         <v>0.93799999999999994</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6">
         <v>1.8391</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6">
         <v>2.2172000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7">
         <v>-0.36580000000000001</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7">
         <v>0.37209999999999999</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7">
         <v>-0.58630000000000004</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7">
         <v>0.9587</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7">
         <v>1.2197</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7">
         <v>0.89229999999999998</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7">
         <v>1.2168000000000001</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7">
         <v>0.89400000000000002</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7">
         <v>0.99239999999999995</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7">
         <v>2.0937999999999999</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7">
         <v>0.36459999999999998</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7">
         <v>0.54920000000000002</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7">
         <v>1.0669999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8">
         <v>-1.0625</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8">
         <v>0.92459999999999998</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8">
         <v>0.1666</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8">
         <v>-0.26960000000000001</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8">
         <v>0.35849999999999999</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8">
         <v>0.95140000000000002</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8">
         <v>0.12330000000000001</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8">
         <v>1.2802</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8">
         <v>-0.68079999999999996</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8">
         <v>0.76339999999999997</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8">
         <v>1.3451</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8">
         <v>0.83550000000000002</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8">
         <v>-0.12709999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9">
         <v>-0.26690000000000003</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9">
         <v>0.37019999999999997</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9">
         <v>-0.61339999999999995</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9">
         <v>1.004</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9">
         <v>-0.14119999999999999</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9">
         <v>-0.37090000000000001</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9">
         <v>0.47349999999999998</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9">
         <v>6.6600000000000006E-2</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9">
         <v>0.61880000000000002</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9">
         <v>-0.2072</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9">
         <v>7.1199999999999999E-2</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9">
         <v>0.55589999999999995</v>
       </c>
-      <c r="N9" s="9">
+      <c r="N9">
         <v>0.58950000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10">
         <v>3.0700000000000002E-2</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10">
         <v>2.1524999999999999</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10">
         <v>1.2788999999999999</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10">
         <v>-0.4526</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10">
         <v>0.69169999999999998</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10">
         <v>0.53420000000000001</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10">
         <v>2.2597999999999998</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10">
         <v>-0.92320000000000002</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10">
         <v>0.82930000000000004</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10">
         <v>1.3828</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10">
         <v>0.90039999999999998</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10">
         <v>0.88880000000000003</v>
       </c>
-      <c r="N10" s="9">
+      <c r="N10">
         <v>-1.0367</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11">
         <v>-1.6758</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11">
         <v>-0.49859999999999999</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11">
         <v>0.38</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11">
         <v>-0.12740000000000001</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11">
         <v>-2.5268999999999999</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11">
         <v>-1.9189000000000001</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11">
         <v>0.54430000000000001</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11">
         <v>8.4500000000000006E-2</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11">
         <v>4.07E-2</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11">
         <v>-1.3691</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11">
         <v>-2.6627000000000001</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11">
         <v>0.20280000000000001</v>
       </c>
-      <c r="N11" s="9">
+      <c r="N11">
         <v>-0.27479999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12">
         <v>-0.92859999999999998</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12">
         <v>-2.3E-2</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12">
         <v>-0.36509999999999998</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12">
         <v>-0.32779999999999998</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12">
         <v>-0.4798</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12">
         <v>0.20469999999999999</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12">
         <v>0.32219999999999999</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12">
         <v>-0.23769999999999999</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12">
         <v>-0.63690000000000002</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12">
         <v>-1.4226000000000001</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12">
         <v>-0.52939999999999998</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12">
         <v>0.29959999999999998</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12">
         <v>0.28120000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13">
         <v>-0.76749999999999996</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13">
         <v>-0.20330000000000001</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13">
         <v>-0.91059999999999997</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13">
         <v>-0.72340000000000004</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13">
         <v>-1.9049</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13">
         <v>0.78539999999999999</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13">
         <v>-0.25700000000000001</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13">
         <v>-0.16869999999999999</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13">
         <v>-1.0667</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13">
         <v>0.1028</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13">
         <v>-2.86E-2</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13">
         <v>0.4798</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13">
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14">
         <v>-1.1269</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14">
         <v>-0.21</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14">
         <v>-0.66759999999999997</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14">
         <v>-1.6963999999999999</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14">
         <v>-0.34960000000000002</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14">
         <v>1.2371000000000001</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14">
         <v>0.94320000000000004</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14">
         <v>-0.36209999999999998</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14">
         <v>-1.8086</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14">
         <v>0.66169999999999995</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14">
         <v>0.61919999999999997</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14">
         <v>0.20499999999999999</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N14">
         <v>-0.72499999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15">
         <v>-0.20250000000000001</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15">
         <v>-1.0587</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15">
         <v>-0.64019999999999999</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15">
         <v>-2.2532000000000001</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15">
         <v>-8.3000000000000004E-2</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15">
         <v>-1.6116999999999999</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15">
         <v>-0.104</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15">
         <v>-0.1487</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15">
         <v>-0.93940000000000001</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15">
         <v>-0.59009999999999996</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15">
         <v>0.13289999999999999</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15">
         <v>-0.72219999999999995</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N15">
         <v>-0.51170000000000004</v>
       </c>
     </row>
@@ -1949,11 +1801,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -1994,569 +1846,569 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="4">
         <v>-0.66849999999999998</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="6">
+      <c r="C2" s="5"/>
+      <c r="D2" s="4">
         <v>-0.43219999999999997</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="4">
         <v>-0.1191</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2">
         <v>-0.38300000000000001</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2">
         <v>0.26929999999999998</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="4">
         <v>-7.5700000000000003E-2</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="4">
         <v>0.59750000000000003</v>
       </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="6">
+      <c r="J2" s="5"/>
+      <c r="K2" s="4">
         <v>-0.3216</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="4">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="4">
         <v>0.4778</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
         <v>-0.3155</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3">
         <v>1.4649000000000001</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>-0.80289999999999995</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>0.5141</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3">
         <v>-0.76539999999999997</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3">
         <v>-1.1456</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="4">
         <v>0.50960000000000005</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="4">
         <v>-0.29570000000000002</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="4">
         <v>-0.22570000000000001</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="4">
         <v>-0.94040000000000001</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="4">
         <v>-1.3326</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="4">
         <v>0.16889999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>0.96209999999999996</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4">
         <v>-0.3518</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>0.31009999999999999</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>-0.15890000000000001</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4">
         <v>0.58689999999999998</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4">
         <v>3.4099999999999998E-2</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <v>0.48599999999999999</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>0.43419999999999997</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <v>1.0717000000000001</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="4">
         <v>5.5899999999999998E-2</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
         <v>1.1548</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="4">
         <v>0.54459999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>6.3299999999999995E-2</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5">
         <v>0.17119999999999999</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>-1.9531000000000001</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>-0.21510000000000001</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5">
         <v>-1.4630000000000001</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5">
         <v>0.30249999999999999</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <v>-2.2646000000000002</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="4">
         <v>1.4417</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
         <v>-1.2318</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="4">
         <v>-0.14030000000000001</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
         <v>-1.9814000000000001</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="4">
         <v>-1.2117</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>-0.91690000000000005</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6">
         <v>1.2958000000000001</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>0.42699999999999999</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>-7.1199999999999999E-2</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6">
         <v>1.5911</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6">
         <v>1.2565999999999999</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <v>0.39100000000000001</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>-0.31259999999999999</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <v>1.5823</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="4">
         <v>2.7766999999999999</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="4">
         <v>0.9466</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="4">
         <v>1.4664999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>9.8199999999999996E-2</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7">
         <v>0.33250000000000002</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>0.29420000000000002</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>5.2299999999999999E-2</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7">
         <v>0.67030000000000001</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7">
         <v>0.71640000000000004</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <v>0.33739999999999998</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <v>0.35539999999999999</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
         <v>6.6400000000000001E-2</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="4">
         <v>1.2329000000000001</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="4">
         <v>0.2175</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="4">
         <v>-0.2056</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="10">
+      <c r="B8" s="5"/>
+      <c r="C8">
         <v>-0.54890000000000005</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>0.24909999999999999</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>0.90359999999999996</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8">
         <v>-0.5302</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8">
         <v>1.6E-2</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>-9.9699999999999997E-2</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="4">
         <v>1.0787</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>-0.1371</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="4">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <v>0.40110000000000001</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="4">
         <v>6.0299999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>0.58789999999999998</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9">
         <v>1.5125</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>0.36570000000000003</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>0.68759999999999999</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9">
         <v>-7.7499999999999999E-2</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9">
         <v>-0.52200000000000002</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <v>0.30730000000000002</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="4">
         <v>-0.36349999999999999</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="4">
         <v>-0.12959999999999999</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="4">
         <v>1.7000999999999999</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="4">
         <v>0.14030000000000001</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="4">
         <v>-4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>1.0931999999999999</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10">
         <v>0.47260000000000002</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>1.1254999999999999</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>0.62629999999999997</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10">
         <v>0.52559999999999996</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10">
         <v>-0.33250000000000002</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="4">
         <v>1.6525000000000001</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="4">
         <v>-0.1135</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="4">
         <v>0.61</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="4">
         <v>0.67210000000000003</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="4">
         <v>0.95820000000000005</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="4">
         <v>0.31269999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>1.2589999999999999</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11">
         <v>1.0717000000000001</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>0.91600000000000004</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <v>0.80400000000000005</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11">
         <v>-1.9025000000000001</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11">
         <v>-0.44059999999999999</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <v>0.56589999999999996</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="4">
         <v>1.258</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="4">
         <v>0.49270000000000003</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="4">
         <v>0.29249999999999998</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="4">
         <v>1.6588000000000001</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="4">
         <v>1.1318999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>-0.4763</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="6">
+      <c r="C12" s="5"/>
+      <c r="D12" s="4">
         <v>-0.33360000000000001</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>-0.54890000000000005</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12">
         <v>2.5266000000000002</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12">
         <v>0.40410000000000001</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <v>2.5700000000000001E-2</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="4">
         <v>-0.2142</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="4">
         <v>-0.31009999999999999</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="4">
         <v>0.90500000000000003</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="4">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="4">
         <v>0.23119999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>-0.1331</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13">
         <v>0.1802</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>-0.32140000000000002</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>-1.8200000000000001E-2</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13">
         <v>0.85260000000000002</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13">
         <v>-0.43319999999999997</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <v>0.22489999999999999</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="4">
         <v>-0.70350000000000001</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="4">
         <v>6.6299999999999998E-2</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="4">
         <v>-0.44190000000000002</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="4">
         <v>0.92220000000000002</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="4">
         <v>0.20899999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>-1.2421</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14">
         <v>0.33439999999999998</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>-0.73499999999999999</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="4">
         <v>0.29349999999999998</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14">
         <v>-1.2684</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14">
         <v>-0.87819999999999998</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="4">
         <v>1.0021</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="4">
         <v>-0.76680000000000004</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="4">
         <v>0.97960000000000003</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="4">
         <v>-5.28E-2</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="4">
         <v>-0.86929999999999996</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="4">
         <v>0.55789999999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>-1.3433999999999999</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15">
         <v>-0.93540000000000001</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <v>-1.7083999999999999</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <v>-0.28220000000000001</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15">
         <v>-5.8900000000000001E-2</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15">
         <v>-0.71579999999999999</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="4">
         <v>-0.11550000000000001</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="4">
         <v>-2.4802</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="4">
         <v>0.66569999999999996</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="4">
         <v>0.53159999999999996</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="4">
         <v>-1.3987000000000001</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="4">
         <v>0.29849999999999999</v>
       </c>
     </row>
@@ -2566,11 +2418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -2611,569 +2463,569 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="4">
         <v>1.452</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="4">
         <v>0.36680000000000001</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>0.14649999999999999</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="4">
         <v>1.0023</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="4">
         <v>1.6619999999999999</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="4">
         <v>2.9944999999999999</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="4">
         <v>1.3996</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="4">
         <v>1.9426000000000001</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="4">
         <v>0.29120000000000001</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="4">
         <v>0.62819999999999998</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="4">
         <v>3.2391000000000001</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="4">
         <v>2.5788000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
         <v>-0.51839999999999997</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>1.3267</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>1.0101</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>-6.1600000000000002E-2</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="6">
+      <c r="F3" s="5"/>
+      <c r="G3" s="4">
         <v>-0.19980000000000001</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="4">
         <v>1.1081000000000001</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="4">
         <v>0.19889999999999999</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="4">
         <v>1.6447000000000001</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="4">
         <v>-1.6053999999999999</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="4">
         <v>0.70450000000000002</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="4">
         <v>0.76729999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>0.59570000000000001</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>0.85489999999999999</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>-0.67589999999999995</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>0.63429999999999997</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>-8.6099999999999996E-2</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>-1.0684</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <v>0.30230000000000001</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>0.41770000000000002</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <v>0.1085</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="4">
         <v>-0.44600000000000001</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
         <v>0.80179999999999996</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="4">
         <v>-0.161</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>3.3136000000000001</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>1.8683000000000001</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>0.90639999999999998</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>0.2848</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>1.2425999999999999</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <v>1.4451000000000001</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <v>0.91479999999999995</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="4">
         <v>-1.32E-2</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
         <v>1.2979000000000001</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="4">
         <v>0.10589999999999999</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
         <v>-0.29759999999999998</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="4">
         <v>0.22559999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>0.97719999999999996</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>1.4618</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>-0.71560000000000001</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>0.78990000000000005</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>1.5734999999999999</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="4">
         <v>1.1125</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <v>1.1015999999999999</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>0.51459999999999995</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <v>1.3432999999999999</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="4">
         <v>0.95009999999999994</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="4">
         <v>1.5648</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="4">
         <v>1.7134</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>0.54879999999999995</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>0.81589999999999996</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>-6.88E-2</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>0.32479999999999998</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>0.32790000000000002</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="4">
         <v>1.2747999999999999</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <v>0.54049999999999998</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <v>0.36120000000000002</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
         <v>0.48139999999999999</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="4">
         <v>-8.1100000000000005E-2</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="4">
         <v>0.31580000000000003</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="4">
         <v>0.80289999999999995</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>1.0774999999999999</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>-1.2575000000000001</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>0.96560000000000001</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>0.16689999999999999</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>0.93940000000000001</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>0.64170000000000005</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>0.58140000000000003</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="4">
         <v>2.5089000000000001</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>0.85389999999999999</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="4">
         <v>1.4608000000000001</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <v>0.77939999999999998</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="4">
         <v>-0.28699999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>1.8202</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>0.32590000000000002</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>-2.2749999999999999</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>6.2700000000000006E-2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>0.2167</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="4">
         <v>0.64400000000000002</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <v>0.54649999999999999</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="4">
         <v>-8.7300000000000003E-2</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="4">
         <v>0.53939999999999999</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="4">
         <v>1.6167</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="4">
         <v>2.0903</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="4">
         <v>0.98519999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>-0.41570000000000001</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>0.88400000000000001</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>1.2987</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>1.3915999999999999</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="4">
         <v>1.0549999999999999</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="4">
         <v>-0.64339999999999997</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="4">
         <v>2.4701</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="4">
         <v>2.3169</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="4">
         <v>1.2747999999999999</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="4">
         <v>1.2483</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="4">
         <v>0.23849999999999999</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="4">
         <v>1.2221</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>0.8397</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>0.85729999999999995</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>0.22919999999999999</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6">
+      <c r="E11" s="5"/>
+      <c r="F11" s="4">
         <v>1.1875</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="4">
         <v>0.21609999999999999</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <v>3.4700000000000002E-2</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="4">
         <v>0.96419999999999995</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="4">
         <v>0.7419</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="4">
         <v>0.10879999999999999</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="4">
         <v>0.65849999999999997</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="4">
         <v>0.2671</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>0.1741</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>-0.5323</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>-1.2532000000000001</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>-8.0500000000000002E-2</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="4">
         <v>-0.3044</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="4">
         <v>0.44</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <v>-1.0186999999999999</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="4">
         <v>-0.56210000000000004</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="4">
         <v>-0.88380000000000003</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="4">
         <v>0.9617</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="4">
         <v>-0.89629999999999999</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="4">
         <v>-0.27239999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>-0.52149999999999996</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>-1.3444</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>0.48070000000000002</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>6.6500000000000004E-2</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="4">
         <v>-5.5100000000000003E-2</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="4">
         <v>-0.29949999999999999</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <v>-0.40570000000000001</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="4">
         <v>-0.4289</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="6">
+      <c r="J13" s="5"/>
+      <c r="K13" s="4">
         <v>-0.99909999999999999</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="4">
         <v>0.47510000000000002</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="4">
         <v>0.2162</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>-0.70220000000000005</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>0.54079999999999995</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>-4.4299999999999999E-2</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="4">
         <v>0.54059999999999997</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="4">
         <v>0.81179999999999997</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="4">
         <v>0.91839999999999999</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="4">
         <v>2.4355000000000002</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="4">
         <v>1.1496</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="4">
         <v>1.0065999999999999</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="4">
         <v>-0.29620000000000002</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="4">
         <v>0.35639999999999999</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="4">
         <v>1.0390999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="6">
+      <c r="B15" s="5"/>
+      <c r="C15" s="4">
         <v>0.56440000000000001</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <v>-1.9400000000000001E-2</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <v>0.82110000000000005</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="4">
         <v>1.1649</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="4">
         <v>0.37130000000000002</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="4">
         <v>0.6099</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="4">
         <v>0.92059999999999997</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="4">
         <v>0.9647</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="4">
         <v>0.49099999999999999</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="4">
         <v>0.92530000000000001</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="4">
         <v>1.2979000000000001</v>
       </c>
     </row>
@@ -3183,11 +3035,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -3228,567 +3080,567 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="4">
         <v>-0.39429999999999998</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="4">
         <v>3.0979999999999999</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>-0.78180000000000005</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="4">
         <v>0.53659999999999997</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="4">
         <v>1.0477000000000001</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="4">
         <v>1.9388000000000001</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="4">
         <v>1.9984999999999999</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="4">
         <v>1.948</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="4">
         <v>2.8677999999999999</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="4">
         <v>3.26</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="4">
         <v>2.2513000000000001</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="4">
         <v>1.9187000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
         <v>1.5094000000000001</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>0.40570000000000001</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>0.59989999999999999</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>1.2909999999999999</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="4">
         <v>1.5787</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="4">
         <v>-0.50419999999999998</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="4">
         <v>1.659</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="4">
         <v>1.728</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="4">
         <v>0.4889</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="4">
         <v>-0.29909999999999998</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="4">
         <v>0.98629999999999995</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="4">
         <v>0.95779999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>-0.41689999999999999</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>0.6492</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>-0.12590000000000001</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>0.71489999999999998</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>4.5699999999999998E-2</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>0.29320000000000002</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <v>-0.3901</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>0.2321</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <v>0.92379999999999995</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="4">
         <v>0.31740000000000002</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
         <v>-2.52E-2</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="4">
         <v>1.0246</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>0.41020000000000001</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>-0.92030000000000001</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>0.37859999999999999</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>-0.81689999999999996</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>3.0099999999999998E-2</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <v>-1.4461999999999999</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <v>-0.30249999999999999</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="4">
         <v>-0.37269999999999998</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
         <v>-0.2195</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="4">
         <v>-1.1638999999999999</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
         <v>0.26190000000000002</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="4">
         <v>-0.52849999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>2.9630999999999998</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>1.0226999999999999</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>-1.8079000000000001</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>2.6496</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="4">
         <v>1.8896999999999999</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <v>1.3274999999999999</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>-2.4363000000000001</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <v>1.3018000000000001</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="4">
         <v>-0.26040000000000002</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="4">
         <v>2.3205</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="4">
         <v>-0.2676</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>0.15079999999999999</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>-0.49149999999999999</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>0.75170000000000003</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>5.9900000000000002E-2</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>0.12920000000000001</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="4">
         <v>0.51680000000000004</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <v>0.4098</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <v>0.48970000000000002</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
         <v>0.37419999999999998</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="4">
         <v>-0.43280000000000002</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="4">
         <v>0.47270000000000001</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="4">
         <v>1.0011000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>0.83460000000000001</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>0.54579999999999995</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>-0.40350000000000003</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>0.5827</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>1.0075000000000001</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>0.80379999999999996</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>1.1451</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="4">
         <v>0.6532</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>1.4213</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="4">
         <v>0.75490000000000002</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <v>0.33239999999999997</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="4">
         <v>0.34039999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>0.94730000000000003</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>0.85960000000000003</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>-0.62880000000000003</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>0.19020000000000001</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>-2.2200000000000001E-2</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="4">
         <v>-8.9499999999999996E-2</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <v>2.07E-2</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="4">
         <v>-0.13739999999999999</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="4">
         <v>0.23630000000000001</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="4">
         <v>0.48659999999999998</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="4">
         <v>-0.49930000000000002</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="4">
         <v>0.58530000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>0.47499999999999998</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>0.89349999999999996</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>3.44E-2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>0.92530000000000001</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="4">
         <v>-0.28220000000000001</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="4">
         <v>0.8125</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="4">
         <v>0.4466</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="4">
         <v>0.3866</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="4">
         <v>-0.1762</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="4">
         <v>0.49059999999999998</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="4">
         <v>0.49409999999999998</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="4">
         <v>0.45229999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>-0.19409999999999999</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>-0.19769999999999999</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>0.32219999999999999</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6">
+      <c r="E11" s="5"/>
+      <c r="F11" s="4">
         <v>0.40579999999999999</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="4">
         <v>-0.84</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <v>0.4143</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="6">
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="4">
         <v>-0.1119</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="4">
         <v>0.41210000000000002</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="4">
         <v>0.16170000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>0.85699999999999998</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>0.39439999999999997</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>-1.01E-2</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>-0.85629999999999995</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="4">
         <v>-0.1573</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="4">
         <v>-0.13389999999999999</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <v>-0.1171</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="6">
+      <c r="I12" s="5"/>
+      <c r="J12" s="4">
         <v>0.3775</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="4">
         <v>0.45390000000000003</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="4">
         <v>0.33310000000000001</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="4">
         <v>0.20960000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="6">
+      <c r="B13" s="5"/>
+      <c r="C13" s="4">
         <v>0.14910000000000001</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>-0.96150000000000002</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>0.69450000000000001</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="4">
         <v>-1.177</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="4">
         <v>0.155</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <v>-1.3154999999999999</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="4">
         <v>-0.11840000000000001</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="4">
         <v>-1.0330999999999999</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="4">
         <v>-0.74029999999999996</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="4">
         <v>0.72799999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>-0.87780000000000002</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>-0.54210000000000003</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>-1.4449000000000001</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="4">
         <v>-0.64190000000000003</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="4">
         <v>-0.98599999999999999</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="4">
         <v>-2.24E-2</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="4">
         <v>-0.44590000000000002</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="4">
         <v>-0.13830000000000001</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="4">
         <v>0.93240000000000001</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="4">
         <v>1.2888999999999999</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="4">
         <v>0.65710000000000002</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="4">
         <v>0.97740000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>-1.7099</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="4">
         <v>-1.3897999999999999</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <v>-2.1356000000000002</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <v>-1.6841999999999999</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="4">
         <v>-0.12379999999999999</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="4">
         <v>-1.0174000000000001</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="4">
         <v>0.37</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="4">
         <v>-1.6722999999999999</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="4">
         <v>-0.25900000000000001</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="4">
         <v>-0.20080000000000001</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="4">
         <v>-1.5284</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="4">
         <v>-1.0412999999999999</v>
       </c>
     </row>
@@ -3798,11 +3650,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:M15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -3843,567 +3695,567 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
         <v>0.62390000000000001</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="4">
         <v>0.81840000000000002</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>1.4916</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="4">
         <v>-0.8397</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="4">
         <v>0.88670000000000004</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="4">
         <v>1.2386999999999999</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="4">
         <v>2.2606000000000002</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="4">
         <v>0.32929999999999998</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="4">
         <v>1.2067000000000001</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="4">
         <v>1.7983</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="4">
         <v>-0.70660000000000001</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="4">
         <v>1.0147999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="4">
         <v>-0.53159999999999996</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="4">
         <v>-0.22209999999999999</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>1.0726</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <v>-0.99180000000000001</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="4">
         <v>0.38919999999999999</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="4">
         <v>0.33529999999999999</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="4">
         <v>-0.29570000000000002</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="4">
         <v>-0.45029999999999998</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="4">
         <v>0.28920000000000001</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="4">
         <v>1.2637</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="4">
         <v>5.0200000000000002E-2</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="4">
         <v>-0.80569999999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>-0.39379999999999998</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>7.8600000000000003E-2</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>-0.97989999999999999</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>0.36030000000000001</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>-0.56820000000000004</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>-7.2800000000000004E-2</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <v>-0.186</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="4">
         <v>0.63060000000000005</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="4">
         <v>0.29170000000000001</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="4">
         <v>-0.1706</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="4">
         <v>0.29249999999999998</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="4">
         <v>0.89139999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>0.2944</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>-1.0325</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>-0.34420000000000001</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>0.89370000000000005</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>-1.5780000000000001</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <v>-1.4498</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <v>-0.73839999999999995</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="4">
         <v>-0.2666</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
         <v>-1.5417000000000001</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="4">
         <v>-3.0545</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="4">
         <v>1.8973</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="4">
         <v>-0.88439999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>1.0058</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="4">
         <v>-3.1699999999999999E-2</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>2.0181</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <v>0.78879999999999995</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>-0.20660000000000001</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="4">
         <v>0.3846</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <v>9.1399999999999995E-2</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="4">
         <v>0.1787</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="4">
         <v>0.1767</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="4">
         <v>0.48980000000000001</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="4">
         <v>0.83540000000000003</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="4">
         <v>0.46439999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>-0.12839999999999999</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="4">
         <v>-0.26989999999999997</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>-0.22539999999999999</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <v>0.74729999999999996</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>0.68830000000000002</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="4">
         <v>-7.1499999999999994E-2</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <v>1.3467</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="4">
         <v>0.60419999999999996</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
         <v>1.385</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="4">
         <v>0.1729</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="4">
         <v>0.1439</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="4">
         <v>0.90949999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>-0.32290000000000002</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="4">
         <v>-0.37169999999999997</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>-0.80130000000000001</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>0.4516</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>-0.37780000000000002</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>-0.32479999999999998</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>-0.47610000000000002</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="4">
         <v>0.95050000000000001</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>-0.2303</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="4">
         <v>-0.56030000000000002</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="4">
         <v>1.2226999999999999</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="4">
         <v>0.57889999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>0.42170000000000002</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="4">
         <v>-1.5840000000000001</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>-2.2523</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>1.9428000000000001</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>2.2200000000000001E-2</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="4">
         <v>-1.5436000000000001</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <v>0.36599999999999999</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="4">
         <v>1.2756000000000001</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="4">
         <v>-0.16350000000000001</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="4">
         <v>-1.1823999999999999</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="4">
         <v>1.5390999999999999</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="4">
         <v>1.5142</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>1.2329000000000001</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="4">
         <v>2.2441</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>0.49480000000000002</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>-0.69450000000000001</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="4">
         <v>-0.83460000000000001</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="4">
         <v>1.8561000000000001</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="4">
         <v>-0.52869999999999995</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="4">
         <v>-0.60660000000000003</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="4">
         <v>0.99839999999999995</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="4">
         <v>1.3966000000000001</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="4">
         <v>-0.15140000000000001</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="4">
         <v>-0.58509999999999995</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>1.5366</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="4">
         <v>0.55740000000000001</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4">
         <v>0.29699999999999999</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="4">
         <v>0.18429999999999999</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <v>0.15820000000000001</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="6">
+      <c r="I11" s="5"/>
+      <c r="J11" s="4">
         <v>1.7097</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="4">
         <v>0.61980000000000002</v>
       </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>0.52490000000000003</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>0.1762</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>-0.16950000000000001</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>0.33610000000000001</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="4">
         <v>1.0117</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="4">
         <v>-0.54710000000000003</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <v>-0.14910000000000001</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="4">
         <v>0.26079999999999998</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="4">
         <v>0.74080000000000001</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="4">
         <v>-0.57830000000000004</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="4">
         <v>0.45569999999999999</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="4">
         <v>0.52290000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>-1.5273000000000001</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="4">
         <v>-4.7899999999999998E-2</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>-0.48859999999999998</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>-4.7199999999999999E-2</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="4">
         <v>-0.37409999999999999</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="4">
         <v>-0.86550000000000005</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <v>-1.1638999999999999</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="4">
         <v>-0.26279999999999998</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="4">
         <v>-0.62990000000000002</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="4">
         <v>6.8199999999999997E-2</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="4">
         <v>0.30349999999999999</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="4">
         <v>-0.54159999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>-0.182</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="4">
         <v>-1.0702</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>-0.84470000000000001</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="4">
         <v>-1.0067999999999999</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="4">
         <v>0.1177</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="4">
         <v>-0.35110000000000002</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="4">
         <v>2.24E-2</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="4">
         <v>-0.61650000000000005</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="4">
         <v>0.77029999999999998</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="4">
         <v>-1.1442000000000001</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="4">
         <v>-0.80579999999999996</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="4">
         <v>0.14030000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>-2.4929000000000001</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="4">
         <v>-0.45329999999999998</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <v>-0.22650000000000001</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <v>-1.1136999999999999</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="4">
         <v>-0.91169999999999995</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="4">
         <v>-0.248</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="4">
         <v>-7.8299999999999995E-2</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="4">
         <v>-1.7543</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="4">
         <v>-0.77810000000000001</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="4">
         <v>-0.3231</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="4">
         <v>0.2596</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="4">
         <v>-2.0924</v>
       </c>
     </row>
@@ -4413,11 +4265,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:O15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4464,7 +4316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4511,7 +4363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -4558,7 +4410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -4605,7 +4457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -4652,7 +4504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -4699,7 +4551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -4746,7 +4598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -4793,7 +4645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -4840,7 +4692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -4887,7 +4739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -4934,7 +4786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -4981,7 +4833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -5028,7 +4880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -5075,7 +4927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -5128,11 +4980,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:O15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5179,7 +5031,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5226,7 +5078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -5273,7 +5125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -5320,7 +5172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -5367,7 +5219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -5414,7 +5266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -5461,7 +5313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -5508,7 +5360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -5555,7 +5407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -5602,7 +5454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -5649,7 +5501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -5696,7 +5548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -5743,7 +5595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -5790,7 +5642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
